--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488113_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488113_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2151</v>
+        <v>7.3245</v>
       </c>
       <c r="E2" t="n">
-        <v>6.324</v>
+        <v>5.1245</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8911</v>
+        <v>2.1999</v>
       </c>
       <c r="G2" t="n">
         <v>5.9884</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3477</v>
+        <v>0.457</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6778</v>
+        <v>0.4783</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3302</v>
+        <v>-0.0213</v>
       </c>
       <c r="V2" t="n">
         <v>1.4737</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>T. PERERIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.548</v>
+        <v>0.6355</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.536</v>
+        <v>-0.484</v>
       </c>
       <c r="F3" t="n">
-        <v>1.084</v>
+        <v>1.1195</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9621</v>
+        <v>2.3183</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1324</v>
+        <v>0.1949</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1703</v>
+        <v>2.1234</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9795</v>
+        <v>1.6645</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2535</v>
+        <v>0.7806</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.274</v>
+        <v>0.8839</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0175</v>
+        <v>0.6538</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1212</v>
+        <v>-0.5857</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1037</v>
+        <v>1.2395</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5769</v>
+        <v>1.1893</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1627</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6187</v>
+        <v>-0.0505</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3706</v>
+        <v>-0.076</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9893</v>
+        <v>0.0255</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5441</v>
+        <v>-2.8216</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0178</v>
+        <v>-1.0813</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4737</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2967</v>
+        <v>0.5971</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0652</v>
+        <v>2.3938</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7685</v>
+        <v>-1.7966</v>
       </c>
       <c r="G4" t="n">
         <v>2.7737</v>
@@ -766,13 +766,13 @@
         <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2611</v>
+        <v>0.0394</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2899</v>
+        <v>0.0386</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0289</v>
+        <v>0.0008</v>
       </c>
       <c r="V4" t="n">
         <v>-2.4142</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. PERERIRA</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2522</v>
+        <v>0.2026</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2595</v>
+        <v>-0.2075</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0072</v>
+        <v>0.4101</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3183</v>
+        <v>0.9621</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1949</v>
+        <v>1.1324</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1234</v>
+        <v>-0.1703</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6645</v>
+        <v>0.9795</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7806</v>
+        <v>2.2535</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8839</v>
+        <v>-1.274</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6538</v>
+        <v>-0.0175</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5857</v>
+        <v>-1.1212</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2395</v>
+        <v>1.1037</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-4.1627</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9383</v>
+        <v>0.2734</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8515</v>
+        <v>-0.0421</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0868</v>
+        <v>0.3154</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.8216</v>
+        <v>1.5441</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.0813</v>
+        <v>3.0178</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7403</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0001</v>
+        <v>-0.4469</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.881</v>
+        <v>-1.5525</v>
       </c>
       <c r="F6" t="n">
-        <v>0.881</v>
+        <v>1.1056</v>
       </c>
       <c r="G6" t="n">
         <v>1.8662</v>
@@ -922,13 +922,13 @@
         <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7166</v>
+        <v>-0.1634</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2972</v>
+        <v>0.0314</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4194</v>
+        <v>-0.1948</v>
       </c>
       <c r="V6" t="n">
         <v>-1.9515</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7366</v>
+        <v>-1.5162</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0332</v>
+        <v>0.131</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7033</v>
+        <v>-1.6472</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5244</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2122</v>
+        <v>0.0083</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1138</v>
+        <v>0.0505</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8898</v>
+        <v>-2.3538</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6602</v>
+        <v>-2.4068</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2296</v>
+        <v>0.0531</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8404</v>
+        <v>0.9769</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1693</v>
+        <v>0.2304</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3289</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.383</v>
+        <v>1.5263</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4232</v>
+        <v>1.4873</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0.0389</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4574</v>
+        <v>-0.5494</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7461</v>
+        <v>-1.257</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2888</v>
+        <v>0.7076</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3876</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1805</v>
+        <v>-3.9645</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.1413</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3634</v>
+        <v>0.0314</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4349</v>
+        <v>-0.1727</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2666</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1316</v>
+        <v>-2.8035</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7354</v>
+        <v>-2.4336</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3962</v>
+        <v>-0.37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9769</v>
+        <v>-1.8404</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2304</v>
+        <v>-2.1693</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.3289</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5263</v>
+        <v>-0.383</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4873</v>
+        <v>-0.4232</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0389</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5494</v>
+        <v>-1.4574</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.257</v>
+        <v>-1.7461</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7076</v>
+        <v>0.2888</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9822</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9645</v>
+        <v>-2.1805</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9191</v>
+        <v>0.1578</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2972</v>
+        <v>-0.1367</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.622</v>
+        <v>0.2945</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.1133</v>
+        <v>-6.7672</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0099</v>
+        <v>-5.355</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1033</v>
+        <v>-1.4122</v>
       </c>
       <c r="G10" t="n">
         <v>-4.7473</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>1.211</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5764</v>
+        <v>0.2313</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.3257</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0638</v>
+        <v>-5.127900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.726</v>
+        <v>-4.790100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3375999999999997</v>
+        <v>-0.3377999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>6.773500000000001</v>
+        <v>6.773499999999999</v>
       </c>
       <c r="H11" t="n">
         <v>-1.3188</v>
@@ -1312,13 +1312,13 @@
         <v>12.8845</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2015999999999998</v>
+        <v>1.1377</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3294000000000001</v>
+        <v>0.6067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5308999999999999</v>
+        <v>0.5309</v>
       </c>
       <c r="V11" t="n">
         <v>-5.11</v>
@@ -1327,7 +1327,7 @@
         <v>2.2585</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.368400000000001</v>
+        <v>-7.368399999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.700699999999999</v>
+        <v>9.9277</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8757</v>
+        <v>7.6907</v>
       </c>
       <c r="F12" t="n">
-        <v>1.825</v>
+        <v>2.237</v>
       </c>
       <c r="G12" t="n">
         <v>5.4047</v>
@@ -1390,13 +1390,13 @@
         <v>3.568</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2829</v>
+        <v>-0.0559</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1121</v>
+        <v>-0.2972</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1708</v>
+        <v>0.2412</v>
       </c>
       <c r="V12" t="n">
         <v>1.0109</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2481</v>
+        <v>3.3548</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0232</v>
+        <v>0.1064</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2249</v>
+        <v>3.2484</v>
       </c>
       <c r="G13" t="n">
         <v>0.7329</v>
@@ -1468,13 +1468,13 @@
         <v>2.7751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7312</v>
+        <v>0.8379</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1125</v>
+        <v>0.1956</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6187</v>
+        <v>0.6422</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.508</v>
+        <v>1.8012</v>
       </c>
       <c r="E14" t="n">
-        <v>1.508</v>
+        <v>2.0067</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="G14" t="n">
-        <v>1.508</v>
+        <v>-0.3415</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3027</v>
+        <v>-0.0069</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2053</v>
+        <v>-0.3346</v>
       </c>
       <c r="J14" t="n">
-        <v>1.508</v>
+        <v>0.9821</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3027</v>
+        <v>0.5246</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2053</v>
+        <v>0.4575</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-1.3237</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.5315</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.7922</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.1496</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.1825</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.3322</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4703</v>
+        <v>1.508</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7999000000000001</v>
+        <v>1.508</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6703</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1198</v>
+        <v>1.508</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0625</v>
+        <v>0.3027</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1823</v>
+        <v>1.2053</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2901</v>
+        <v>1.508</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.3027</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2896</v>
+        <v>1.2053</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1704</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0631</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1073</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2316</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1749</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3036</v>
+        <v>1.2107</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7011</v>
+        <v>1.2107</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3974</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3415</v>
+        <v>1.2107</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0069</v>
+        <v>1.2107</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3346</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9821</v>
+        <v>1.2107</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5246</v>
+        <v>1.2107</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4575</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3237</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5315</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7922</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.348</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4881</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1402</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2107</v>
+        <v>0.8588</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2107</v>
+        <v>1.4749</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.616</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2107</v>
+        <v>-0.8053</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2107</v>
+        <v>-0.8071</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2107</v>
+        <v>0.4503</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2107</v>
+        <v>0.3298</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.2556</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.1369</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.1187</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.1376</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.1825</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0449</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3027</v>
+        <v>0.7866</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3027</v>
+        <v>-0.015</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.8016</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3027</v>
+        <v>0.1198</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3027</v>
+        <v>-1.0625</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.1823</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3027</v>
+        <v>1.2901</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3027</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.2896</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.1704</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.0631</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.1073</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.3599</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2209</v>
+        <v>0.3027</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1692</v>
+        <v>0.3027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9484</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8053</v>
+        <v>0.3027</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8071</v>
+        <v>0.3027</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0018</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4503</v>
+        <v>0.3027</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3298</v>
+        <v>0.3027</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2556</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1369</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1187</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7756</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4881</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2875</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2917</v>
+        <v>-0.2682</v>
       </c>
       <c r="E20" t="n">
         <v>-1.3923</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1006</v>
+        <v>1.1241</v>
       </c>
       <c r="G20" t="n">
         <v>-2.124</v>
@@ -2014,13 +2014,13 @@
         <v>2.7751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5308</v>
+        <v>0.5543</v>
       </c>
       <c r="T20" t="n">
         <v>-0.121</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6518</v>
+        <v>0.6753</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4737</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4249</v>
+        <v>-1.5182</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9956</v>
+        <v>-4.5287</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4294</v>
+        <v>3.0105</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.035</v>
+        <v>-3.1999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2717</v>
+        <v>-2.1841</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7634</v>
+        <v>-1.0158</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3092</v>
+        <v>-1.9618</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3298</v>
+        <v>-0.6515</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.639</v>
+        <v>-1.3103</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7258</v>
+        <v>-1.2381</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6014</v>
+        <v>-1.5326</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1244</v>
+        <v>0.2945</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3964</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-4.9556</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5947</v>
+        <v>2.9733</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2731</v>
+        <v>-0.0982</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3047</v>
+        <v>-0.0255</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0316</v>
+        <v>-0.0727</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2666</v>
+        <v>3.7621</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2666</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5062</v>
+        <v>-1.7632</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9361</v>
+        <v>-1.3012</v>
       </c>
       <c r="F22" t="n">
-        <v>2.43</v>
+        <v>-0.462</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1999</v>
+        <v>-1.035</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1841</v>
+        <v>-0.2717</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0158</v>
+        <v>-0.7634</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9618</v>
+        <v>-0.3092</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6515</v>
+        <v>0.3298</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3103</v>
+        <v>-0.639</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2381</v>
+        <v>-0.7258</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5326</v>
+        <v>-0.6014</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2945</v>
+        <v>-0.1244</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9822</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.9556</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9733</v>
+        <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0862</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.433</v>
+        <v>-0.0009</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6532</v>
+        <v>-0.0643</v>
       </c>
       <c r="V22" t="n">
-        <v>3.7621</v>
+        <v>-0.2666</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.3479</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2213</v>
+        <v>-3.8406</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2293</v>
+        <v>-3.9237</v>
       </c>
       <c r="F23" t="n">
-        <v>0.008</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-5.9464</v>
@@ -2248,13 +2248,13 @@
         <v>3.1716</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6009</v>
+        <v>-0.2202</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6202</v>
+        <v>-0.3146</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0193</v>
+        <v>0.0944</v>
       </c>
       <c r="V23" t="n">
         <v>1.1367</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.457</v>
+        <v>-4.2591</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6994</v>
+        <v>-2.8012</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7576</v>
+        <v>-1.4579</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1252</v>
+        <v>0.3231</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1396</v>
+        <v>0.0377</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0144</v>
+        <v>0.2854</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.063900000000001</v>
+        <v>8.101199999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3378000000000023</v>
+        <v>0.3380000000000005</v>
       </c>
       <c r="F25" t="n">
-        <v>5.726</v>
+        <v>7.763300000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-6.773300000000001</v>
@@ -2383,7 +2383,7 @@
         <v>11.31</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.925</v>
+        <v>-4.925000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-13.1583</v>
@@ -2395,7 +2395,7 @@
         <v>-3.1674</v>
       </c>
       <c r="P25" t="n">
-        <v>7.929000000000001</v>
+        <v>7.928999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.8844</v>
@@ -2404,13 +2404,13 @@
         <v>20.8134</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2016999999999997</v>
+        <v>1.8357</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5307999999999999</v>
+        <v>-0.531</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3292000000000001</v>
+        <v>2.3666</v>
       </c>
       <c r="V25" t="n">
         <v>5.109900000000001</v>
